--- a/artfynd/A 24950-2026 artfynd.xlsx
+++ b/artfynd/A 24950-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134180791</v>
+        <v>134298136</v>
       </c>
       <c r="B2" t="n">
-        <v>58136</v>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 24950/51, Solhem, Sm</t>
+          <t>A 24950, Solhem, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588524</v>
+        <v>588406</v>
       </c>
       <c r="R2" t="n">
-        <v>6399625</v>
+        <v>6399674</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -752,12 +751,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +770,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -784,42 +789,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134298115</v>
+        <v>134298177</v>
       </c>
       <c r="B3" t="n">
-        <v>57972</v>
+        <v>92188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>3008</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -827,13 +835,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588407</v>
+        <v>588470</v>
       </c>
       <c r="R3" t="n">
-        <v>6399696</v>
+        <v>6399644</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,17 +873,13 @@
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår efter födosök, stubbe</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -894,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134303755</v>
+        <v>134298115</v>
       </c>
       <c r="B4" t="n">
-        <v>57162</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +909,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,23 +931,23 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Solhem, Sm</t>
+          <t>A 24950, Solhem, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588521</v>
+        <v>588407</v>
       </c>
       <c r="R4" t="n">
-        <v>6399521</v>
+        <v>6399696</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -967,22 +971,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>20:30</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>20:30</t>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår efter födosök, stubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,72 +996,68 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ante Hultgren</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134298198</v>
+        <v>134303755</v>
       </c>
       <c r="B5" t="n">
-        <v>58136</v>
+        <v>57162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>A 24950, Solhem, Sm</t>
+          <t>Solhem, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588469</v>
+        <v>588521</v>
       </c>
       <c r="R5" t="n">
-        <v>6399653</v>
+        <v>6399521</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,12 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,19 +1111,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Ante Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134298110</v>
+        <v>134180791</v>
       </c>
       <c r="B6" t="n">
         <v>58136</v>
@@ -1148,27 +1153,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>pulli/nyligen flygga ungar</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>A 24950, Solhem, Sm</t>
+          <t>A 24950/51, Solhem, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588407</v>
+        <v>588524</v>
       </c>
       <c r="R6" t="n">
-        <v>6399696</v>
+        <v>6399625</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1195,17 +1200,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Familjegrupp med utflugna ungar. Ungarna tiggde.</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,6 +1229,229 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134298110</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 24950, Solhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>588407</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6399696</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Familjegrupp med utflugna ungar. Ungarna tiggde.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134298198</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 24950, Solhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>588469</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6399653</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gladhammar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
